--- a/Pruebas calificadas/COLEGIO-LUIS-EDUARDO-MORA-OSEJO-(IED)-1103__CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LUIS-EDUARDO-MORA-OSEJO-(IED)-1103__CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -980,11 +976,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -992,7 +984,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1225,11 +1217,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1237,7 +1225,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1478,11 +1466,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1490,7 +1474,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1731,11 +1715,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1743,7 +1723,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1984,11 +1964,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1996,7 +1972,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2237,11 +2213,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2249,7 +2221,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2490,11 +2462,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2502,7 +2470,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2743,11 +2711,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2755,7 +2719,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2996,11 +2960,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3008,7 +2968,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3249,11 +3209,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3261,7 +3217,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3498,11 +3454,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3510,7 +3462,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3751,11 +3703,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3763,7 +3711,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4004,11 +3952,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4016,7 +3960,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4257,11 +4201,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4269,7 +4209,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4510,11 +4450,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4522,7 +4458,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4763,11 +4699,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4775,7 +4707,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5016,11 +4948,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5028,7 +4956,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5269,11 +5197,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5281,7 +5205,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5522,11 +5446,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5534,7 +5454,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5775,11 +5695,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5787,7 +5703,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6028,11 +5944,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6040,7 +5952,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6281,11 +6193,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6293,7 +6201,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6534,11 +6442,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6546,7 +6450,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6787,11 +6691,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6799,7 +6699,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7040,11 +6940,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7052,7 +6948,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7293,11 +7189,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7305,7 +7197,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7546,11 +7438,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7558,7 +7446,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7799,11 +7687,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7811,7 +7695,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8052,11 +7936,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -8064,7 +7944,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8305,11 +8185,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -8317,7 +8193,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8558,11 +8434,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -8570,7 +8442,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8811,11 +8683,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -8823,7 +8691,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9064,11 +8932,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -9076,7 +8940,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9317,11 +9181,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -9329,7 +9189,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9570,11 +9430,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -9582,7 +9438,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9823,11 +9679,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -9835,7 +9687,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10076,11 +9928,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -10088,7 +9936,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10325,11 +10173,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -10337,7 +10181,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10574,11 +10418,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -10586,7 +10426,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10827,11 +10667,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -10839,7 +10675,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11080,11 +10916,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -11092,7 +10924,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11333,11 +11165,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -11345,7 +11173,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11586,11 +11414,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -11598,7 +11422,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11839,11 +11663,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -11851,7 +11671,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12092,11 +11912,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -12104,7 +11920,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
